--- a/RES/tables/descriptive_statistics.xlsx
+++ b/RES/tables/descriptive_statistics.xlsx
@@ -509,10 +509,10 @@
         <v>23</v>
       </c>
       <c r="B2" t="n">
-        <v>36.68</v>
+        <v>37.83</v>
       </c>
       <c r="C2" t="n">
-        <v>15.101</v>
+        <v>15.741</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
